--- a/TabeleExcel/Tabele_UserFriendly/Salary_history.xlsx
+++ b/TabeleExcel/Tabele_UserFriendly/Salary_history.xlsx
@@ -190,15 +190,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -536,7 +536,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>42024</v>
+        <v>41294</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -596,7 +596,7 @@
         <v>3800</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>43840</v>
+        <v>43475</v>
       </c>
       <c r="E16" s="1"/>
     </row>

--- a/TabeleExcel/Tabele_UserFriendly/Salary_history.xlsx
+++ b/TabeleExcel/Tabele_UserFriendly/Salary_history.xlsx
@@ -393,6 +393,9 @@
   </sheetPr>
   <dimension ref="B1:E28"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.64"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
@@ -689,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>44722</v>
